--- a/packages/connectors/src/exports/__fixtures__/jobber-timesheets.sample.xlsx
+++ b/packages/connectors/src/exports/__fixtures__/jobber-timesheets.sample.xlsx
@@ -56,7 +56,7 @@
     <t>Avery Reed</t>
   </si>
   <si>
-    <t>Client Alpha</t>
+    <t>Brookside Dental</t>
   </si>
   <si>
     <t>Job #101 - Spring cleanup</t>
@@ -74,7 +74,7 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>Client Beta</t>
+    <t>Maple Grove HOA</t>
   </si>
   <si>
     <t>Job #102 - Total care</t>
